--- a/artfynd/A 61654-2025 artfynd.xlsx
+++ b/artfynd/A 61654-2025 artfynd.xlsx
@@ -2297,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130938729</v>
+        <v>130938723</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>83224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,31 +2308,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2340,10 +2335,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476618</v>
+        <v>476289</v>
       </c>
       <c r="R15" t="n">
-        <v>7033500</v>
+        <v>7033519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2378,17 +2373,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2407,14 +2398,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2432,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130938723</v>
+        <v>130938729</v>
       </c>
       <c r="B16" t="n">
-        <v>83224</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,26 +2429,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2470,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476289</v>
+        <v>476618</v>
       </c>
       <c r="R16" t="n">
-        <v>7033519</v>
+        <v>7033500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2508,13 +2499,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2533,9 +2528,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130938731</v>
+        <v>130938751</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,31 +3438,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3470,10 +3465,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476549</v>
+        <v>476394</v>
       </c>
       <c r="R24" t="n">
-        <v>7033604</v>
+        <v>7033617</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3508,17 +3503,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3557,7 +3548,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130938751</v>
+        <v>130938746</v>
       </c>
       <c r="B25" t="n">
         <v>79244</v>
@@ -3595,10 +3586,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476394</v>
+        <v>476419</v>
       </c>
       <c r="R25" t="n">
-        <v>7033617</v>
+        <v>7033605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3678,10 +3669,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130938746</v>
+        <v>130938731</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3689,26 +3680,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3716,10 +3712,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476419</v>
+        <v>476549</v>
       </c>
       <c r="R26" t="n">
-        <v>7033605</v>
+        <v>7033604</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3754,13 +3750,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61654-2025 artfynd.xlsx
+++ b/artfynd/A 61654-2025 artfynd.xlsx
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130938745</v>
+        <v>130938749</v>
       </c>
       <c r="B8" t="n">
         <v>79244</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476596</v>
+        <v>476536</v>
       </c>
       <c r="R8" t="n">
-        <v>7033587</v>
+        <v>7033595</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130938749</v>
+        <v>130938745</v>
       </c>
       <c r="B9" t="n">
         <v>79244</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476536</v>
+        <v>476596</v>
       </c>
       <c r="R9" t="n">
-        <v>7033595</v>
+        <v>7033587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130938723</v>
+        <v>130938729</v>
       </c>
       <c r="B15" t="n">
-        <v>83224</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,26 +2308,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2335,10 +2340,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476289</v>
+        <v>476618</v>
       </c>
       <c r="R15" t="n">
-        <v>7033519</v>
+        <v>7033500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2373,13 +2378,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2398,9 +2407,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2418,10 +2432,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130938729</v>
+        <v>130938723</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>83224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,31 +2443,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2461,10 +2470,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476618</v>
+        <v>476289</v>
       </c>
       <c r="R16" t="n">
-        <v>7033500</v>
+        <v>7033519</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2499,17 +2508,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2528,14 +2533,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130938743</v>
+        <v>130938740</v>
       </c>
       <c r="B17" t="n">
-        <v>91829</v>
+        <v>78256</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2564,26 +2564,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476555</v>
+        <v>476532</v>
       </c>
       <c r="R17" t="n">
-        <v>7033581</v>
+        <v>7033586</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2642,21 +2642,6 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2674,10 +2659,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130938740</v>
+        <v>130938743</v>
       </c>
       <c r="B18" t="n">
-        <v>78256</v>
+        <v>91829</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2685,26 +2670,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2712,10 +2697,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476532</v>
+        <v>476555</v>
       </c>
       <c r="R18" t="n">
-        <v>7033586</v>
+        <v>7033581</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2763,6 +2748,21 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2780,10 +2780,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130938752</v>
+        <v>130938734</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2791,26 +2791,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2818,10 +2823,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476286</v>
+        <v>476457</v>
       </c>
       <c r="R19" t="n">
-        <v>7033527</v>
+        <v>7033634</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2856,13 +2861,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2881,9 +2890,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2901,10 +2915,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130938734</v>
+        <v>130938752</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2912,31 +2926,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2944,10 +2953,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476457</v>
+        <v>476286</v>
       </c>
       <c r="R20" t="n">
-        <v>7033634</v>
+        <v>7033527</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2982,17 +2991,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3011,14 +3016,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130938751</v>
+        <v>130938731</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,26 +3438,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3465,10 +3470,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476394</v>
+        <v>476549</v>
       </c>
       <c r="R24" t="n">
-        <v>7033617</v>
+        <v>7033604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3503,13 +3508,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3548,7 +3557,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130938746</v>
+        <v>130938751</v>
       </c>
       <c r="B25" t="n">
         <v>79244</v>
@@ -3586,10 +3595,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476419</v>
+        <v>476394</v>
       </c>
       <c r="R25" t="n">
-        <v>7033605</v>
+        <v>7033617</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3669,10 +3678,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130938731</v>
+        <v>130938746</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3680,31 +3689,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3712,10 +3716,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476549</v>
+        <v>476419</v>
       </c>
       <c r="R26" t="n">
-        <v>7033604</v>
+        <v>7033605</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3750,17 +3754,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61654-2025 artfynd.xlsx
+++ b/artfynd/A 61654-2025 artfynd.xlsx
@@ -1052,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130938725</v>
+        <v>130938736</v>
       </c>
       <c r="B5" t="n">
-        <v>91809</v>
+        <v>58043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,41 +1063,50 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stensvågen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476460</v>
+        <v>476389</v>
       </c>
       <c r="R5" t="n">
-        <v>7033592</v>
+        <v>7033614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1138,33 +1147,12 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1182,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130938736</v>
+        <v>130938725</v>
       </c>
       <c r="B6" t="n">
-        <v>58043</v>
+        <v>91809</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,50 +1181,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stensvågen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476389</v>
+        <v>476460</v>
       </c>
       <c r="R6" t="n">
-        <v>7033614</v>
+        <v>7033592</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,12 +1256,33 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1421,7 +1421,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130938749</v>
+        <v>130938745</v>
       </c>
       <c r="B8" t="n">
         <v>79244</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476536</v>
+        <v>476596</v>
       </c>
       <c r="R8" t="n">
-        <v>7033595</v>
+        <v>7033587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130938745</v>
+        <v>130938749</v>
       </c>
       <c r="B9" t="n">
         <v>79244</v>
@@ -1580,10 +1580,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476596</v>
+        <v>476536</v>
       </c>
       <c r="R9" t="n">
-        <v>7033587</v>
+        <v>7033595</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130938729</v>
+        <v>130938723</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>83224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,31 +2308,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2340,10 +2335,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476618</v>
+        <v>476289</v>
       </c>
       <c r="R15" t="n">
-        <v>7033500</v>
+        <v>7033519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2378,17 +2373,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2407,14 +2398,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2432,10 +2418,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130938723</v>
+        <v>130938729</v>
       </c>
       <c r="B16" t="n">
-        <v>83224</v>
+        <v>57884</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,26 +2429,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2470,10 +2461,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476289</v>
+        <v>476618</v>
       </c>
       <c r="R16" t="n">
-        <v>7033519</v>
+        <v>7033500</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2508,13 +2499,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2533,9 +2528,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3427,10 +3427,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130938731</v>
+        <v>130938751</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3438,31 +3438,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3470,10 +3465,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476549</v>
+        <v>476394</v>
       </c>
       <c r="R24" t="n">
-        <v>7033604</v>
+        <v>7033617</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3508,17 +3503,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3557,7 +3548,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130938751</v>
+        <v>130938746</v>
       </c>
       <c r="B25" t="n">
         <v>79244</v>
@@ -3595,10 +3586,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476394</v>
+        <v>476419</v>
       </c>
       <c r="R25" t="n">
-        <v>7033617</v>
+        <v>7033605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3678,10 +3669,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130938746</v>
+        <v>130938731</v>
       </c>
       <c r="B26" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3689,26 +3680,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3716,10 +3712,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476419</v>
+        <v>476549</v>
       </c>
       <c r="R26" t="n">
-        <v>7033605</v>
+        <v>7033604</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3754,13 +3750,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 61654-2025 artfynd.xlsx
+++ b/artfynd/A 61654-2025 artfynd.xlsx
@@ -813,7 +813,7 @@
         <v>130938742</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>130938748</v>
       </c>
       <c r="B4" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1052,10 +1052,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130938736</v>
+        <v>130938725</v>
       </c>
       <c r="B5" t="n">
-        <v>58043</v>
+        <v>91810</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,50 +1063,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stensvågen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476389</v>
+        <v>476460</v>
       </c>
       <c r="R5" t="n">
-        <v>7033614</v>
+        <v>7033592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,12 +1138,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1170,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130938725</v>
+        <v>130938736</v>
       </c>
       <c r="B6" t="n">
-        <v>91809</v>
+        <v>58043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,41 +1193,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stensvågen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476460</v>
+        <v>476389</v>
       </c>
       <c r="R6" t="n">
-        <v>7033592</v>
+        <v>7033614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,33 +1277,12 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
         <v>130938750</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         <v>130938745</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>130938749</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>130938747</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         <v>130938744</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>130938723</v>
       </c>
       <c r="B15" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130938740</v>
+        <v>130938743</v>
       </c>
       <c r="B17" t="n">
-        <v>78256</v>
+        <v>91830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2564,26 +2564,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Tibell</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476532</v>
+        <v>476555</v>
       </c>
       <c r="R17" t="n">
-        <v>7033586</v>
+        <v>7033581</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2642,6 +2642,21 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2659,10 +2674,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130938743</v>
+        <v>130938740</v>
       </c>
       <c r="B18" t="n">
-        <v>91829</v>
+        <v>78257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,26 +2685,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2697,10 +2712,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476555</v>
+        <v>476532</v>
       </c>
       <c r="R18" t="n">
-        <v>7033581</v>
+        <v>7033586</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2748,21 +2763,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2918,7 +2918,7 @@
         <v>130938752</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130938728</v>
+        <v>130938724</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>83225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,31 +3047,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3079,10 +3074,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476499</v>
+        <v>476565</v>
       </c>
       <c r="R21" t="n">
-        <v>7033819</v>
+        <v>7033670</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3117,17 +3112,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3146,14 +3137,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3171,10 +3157,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130938724</v>
+        <v>130938728</v>
       </c>
       <c r="B22" t="n">
-        <v>83224</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3182,26 +3168,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3209,10 +3200,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476565</v>
+        <v>476499</v>
       </c>
       <c r="R22" t="n">
-        <v>7033670</v>
+        <v>7033819</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3247,13 +3238,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3272,9 +3267,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
         <v>130938751</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>130938746</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 61654-2025 artfynd.xlsx
+++ b/artfynd/A 61654-2025 artfynd.xlsx
@@ -2297,10 +2297,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130938723</v>
+        <v>130938729</v>
       </c>
       <c r="B15" t="n">
-        <v>83225</v>
+        <v>57884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2308,26 +2308,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2335,10 +2340,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476289</v>
+        <v>476618</v>
       </c>
       <c r="R15" t="n">
-        <v>7033519</v>
+        <v>7033500</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2373,13 +2378,17 @@
           <t>2026-01-24</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2398,9 +2407,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2418,10 +2432,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130938729</v>
+        <v>130938723</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>83225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2429,31 +2443,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2461,10 +2470,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476618</v>
+        <v>476289</v>
       </c>
       <c r="R16" t="n">
-        <v>7033500</v>
+        <v>7033519</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2499,17 +2508,13 @@
           <t>2026-01-24</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2528,14 +2533,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
